--- a/docs/planning/QA엑셀-v1/이혜린/QA 담양 중대재해 인력·예산 이혜린.xlsx
+++ b/docs/planning/QA엑셀-v1/이혜린/QA 담양 중대재해 인력·예산 이혜린.xlsx
@@ -11,19 +11,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인력 평가" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="평가 현황·설정" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예산 총괄표" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예산 기준 설정" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예산 기준 설정" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예산 총괄표" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_정보" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'인력 평가'!$A$3:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'인력 평가'!$A$3:$I$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'인력 평가'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'평가 현황·설정'!$A$3:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'평가 현황·설정'!$A$3:$I$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'평가 현황·설정'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'예산 총괄표'!$A$3:$I$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'예산 총괄표'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'예산 기준 설정'!$A$3:$I$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'예산 기준 설정'!$3:$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'예산 기준 설정'!$A$3:$I$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'예산 기준 설정'!$3:$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'예산 총괄표'!$A$3:$I$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'예산 총괄표'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,9 +58,9 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="000563C1"/>
       <sz val="10.5"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -113,6 +113,12 @@
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00A6A6A6"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
       <sz val="10.5"/>
     </font>
   </fonts>
@@ -289,7 +295,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -787,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -846,12 +852,12 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>이 파일</t>
+          <t>내 계정</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>인력 평가(인력 평가 · 평가 현황 · 평가 설정)와 예산 관리(예산 총괄표 · 예산 기준 설정)를 봅니다. 상신은 담당자만 합니다.</t>
+          <t>QA박안전6 (재난안전과 담당자) · QA하정수6 (내 부서 문화체육과 담당 공무원)</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -861,15 +867,15 @@
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>줄 수</t>
+          <t>이 파일</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>15줄</t>
+          <t>인력 평가(인력 평가 · 평가 현황 · 평가 설정)와 예산 관리(예산 기준 설정 · 예산 총괄표)를 봅니다. 대부분 QA박안전6 계정으로 하고, 평가·점검표는 내 부서(문화체육과) 것만 만듭니다.</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -882,12 +888,12 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>시트</t>
+          <t>줄 수</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>인력 평가 → 평가 현황·설정 → 예산 총괄표 → 예산 기준 설정</t>
+          <t>23줄</t>
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -900,12 +906,12 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>테스트 주소</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>(배포 주소를 받으면 채웁니다)</t>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>인력 평가 → 평가 현황·설정 → 예산 기준 설정 → 예산 총괄표</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -918,10 +924,14 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>브라우저</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
+          <t>테스트 주소</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>https://safety.damyang.go.kr/login</t>
+        </is>
+      </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
@@ -932,7 +942,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>기기</t>
+          <t>브라우저</t>
         </is>
       </c>
       <c r="B10" s="7" t="n"/>
@@ -946,10 +956,10 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>시작한 날</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
+          <t>기기</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
@@ -957,82 +967,78 @@
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>시작한 날</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>이렇게 하면 됩니다</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>① 브라우저로 위 «테스트 주소»를 엽니다. 시트마다 맨 위에 «새 탭에서 시작» 또는 «같은 탭에서 이어서»가 적혀 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1">
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>② 화면 오른쪽 위 이름을 눌러 «누구로» 칸의 사람으로 바꿉니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1">
+          <t>① 위 «테스트 주소»에서 받은 아이디·비밀번호로 로그인합니다. 로그인하면 통합 현황 화면으로 갑니다. 5번 틀리면 계정이 잠깁니다 — 담당 개발자에게 풀어 달라고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>③ «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
+          <t>② 내 계정 두 개를 창 두 개에 따로 로그인해 둡니다 — 일반 창에는 QA박안전6(재난안전과), 시크릿 창(Ctrl + Shift + N · 맥 Cmd + Shift + N)에는 QA하정수6(담당 공무원). 두 창을 나란히 두면 계정을 바꿀 필요가 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+          <t>③ «누구로» 칸에 적힌 계정의 창에서 «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
           <t>⑤ 실패·오류·문의면 «메모»에 한 줄 적고, 필요하면 «사진» 칸에 화면 캡처를 붙여넣습니다.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>결과 고르는 법</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>결과</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>이럴 때 고르세요</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>«이러면 성공»대로 된다</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -1043,14 +1049,14 @@
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>실패</t>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>성공</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
+          <t>«이러면 성공»대로 된다</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
@@ -1061,14 +1067,14 @@
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>오류</t>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>실패</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
+          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -1079,14 +1085,14 @@
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>보류</t>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>오류</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
+          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
@@ -1097,14 +1103,14 @@
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>보류</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
+          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
@@ -1115,14 +1121,14 @@
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>문의</t>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
+          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
@@ -1132,256 +1138,216 @@
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>사진 붙이는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
+          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
+          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
+          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
           <t>• 사진은 떠 있는 그대로 두세요(«셀에 배치»로 넣으면 취합할 때 꺼내지 못합니다).</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>누구로 — 계정 바꾸는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="21" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>• 화면 오른쪽 위 이름을 누르면 사람 목록이 나옵니다. «누구로» 칸의 이름을 누르면 바뀝니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>누구로 — 내 계정 두 개</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>• 계정은 두 개뿐입니다. «누구로» 칸에 계정 이름과 권한이 함께 적혀 있습니다. 비밀번호는 따로 받습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>누구</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>권한</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>볼 수 있는 것</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>주로 하는 것</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>재난안전과 담당자</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>대부분 이 계정 — 등록·확인·공문</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="5" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA박안전6</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소 담당자</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서 일만 한다</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n"/>
+          <t>재난안전과 담당자</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>모든 부서 · «내 할일»은 전체</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>전 부서 등록·수정 · 확인 · 상신 · 독촉 — 대부분 이 계정</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="5" t="n"/>
     </row>
-    <row r="40" ht="22" customHeight="1">
+    <row r="40" ht="51" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>정환경</t>
+          <t>QA하정수6</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>환경과 담당자</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>남의 부서 것을 못 건드리는지 볼 때</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n"/>
+          <t>담당 공무원 (내 부서: 문화체육과)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>업무 화면은 전 부서, «내 할일»은 나에게 지정된 것만, 위험성평가 부서별 조치표·교육 이수현황은 내 부서만</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>내 부서 일 · 남의 부서 것을 못 건드리는지 확인</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="5" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>오순환</t>
+          <t>QA시스템관리</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소장</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서를 보고 재촉한다</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n"/>
+          <t>시스템 관리자 (김유석만)</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 메뉴</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 파일 · 공문 반려(결재 대행)</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="5" t="n"/>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>김중대</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>중대재해팀장</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>공문 결재선(검토)을 볼 때</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>재난안전과장</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다 — 등록 버튼이 없는 게 정상</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>김담양</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>군수</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="5" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>같은 서버를 6명이 함께 씁니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>• 내가 만드는 것(교육 · 근로자 · 문서 · 위원 등)은 이름 앞에 내 이름을 붙입니다 — 예: «이혜린_집합교육». 그래야 내 것을 찾기 쉽습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>• 다른 사람이 만든 것은 고치거나 지우지 않습니다. QA박안전6 계정에는 남의 것도 보이는데, 정상입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>• 건수·이수율 같은 숫자는 다른 사람이 작업하는 동안 바뀔 수 있습니다. 숫자가 안 맞으면 새로고침해서 한 번 더 보고, 그래도 다르면 «실패».</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>알아 두면 좋은 것 (결함이 아닙니다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="21" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>• 오늘 날짜가 2026-07-16 으로 고정돼 있습니다. 기한·D-day는 이 날 기준입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="21" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>• 입력한 데이터는 그 브라우저 탭에만 남습니다. 새 탭을 열면 처음 상태로 돌아갑니다(새로고침은 괜찮습니다).</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>• 파일 첨부는 파일 이름만 남습니다. 실제 파일을 열거나 받을 수는 없습니다.</t>
+          <t>• 기한·D-day는 서버의 오늘 날짜 기준입니다.</t>
         </is>
       </c>
     </row>
@@ -1395,85 +1361,110 @@
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>• 과장·군수에게 등록·수정 버튼이 없는 것, 결재 승인·반려 버튼이 없는 것(결재는 온나라에서 합니다)은 정상입니다.</t>
+          <t>• «이러면 성공»의 «» 안 문구와 화면 글자가 조금 다르고(띄어쓰기·마침표·어순) 뜻이 같으면 «문의»로 고르고 화면 문구를 메모에 적습니다.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>• 2025년 자료는 실제 문서이고, 2026년 자료는 «예시 자료»입니다.</t>
+          <t>• 온나라 연계 전까지 결재는 시스템 안에서 끝납니다 — 상신하면 바로 «결재완료»가 되고 «내부 처리»로 표시됩니다. 결재자가 로그인해 승인할 일은 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>• ---</t>
+          <t>• 로그인은 30분이 지나면 끊깁니다(작업 중이어도). 다시 로그인하고 이어서 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>• 독촉·재촉 알림은 실제 직원에게 가고 되돌릴 수 없습니다. 내 부서 건만 1건씩 누릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>• 과장·팀장이 담당자를 지정하는 흐름과 «내 할일»의 ‹자기 부서 전체› 보기는 과장 계정이 없어 이번 QA 범위 밖입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>• 순서를 놓쳤거나 확인할 자료가 서버에 없으면 «확인 불가»를 고르고 메모에 이유를 적습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A30:H30"/>
+  <mergeCells count="51">
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A49:H49"/>
-    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="D40:E40"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="F38:H38"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A54:H54"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B25:H25"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="A50:H50"/>
-    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="B12:H12"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A47:H47"/>
     <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="B23:H23"/>
     <mergeCell ref="A17:H17"/>
+    <mergeCell ref="D39:E39"/>
     <mergeCell ref="B8:H8"/>
-    <mergeCell ref="E40:H40"/>
     <mergeCell ref="A53:H53"/>
     <mergeCell ref="A52:H52"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"크롬,엣지,웨일,사파리,파이어폭스,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"윈도우 PC,맥,태블릿,휴대폰"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1573,36 +1564,36 @@
         </is>
       </c>
       <c r="B5" s="21">
-        <f>COUNTA('인력 평가'!$A$4:$A$8)</f>
-        <v>5</v>
+        <f>COUNTA('인력 평가'!$A$4:$A$9)</f>
+        <v>6</v>
       </c>
       <c r="C5" s="21">
-        <f>COUNTIF('인력 평가'!$G$4:$G$8,"성공")</f>
+        <f>COUNTIF('인력 평가'!$G$4:$G$9,"성공")</f>
         <v>0</v>
       </c>
       <c r="D5" s="21">
-        <f>COUNTIF('인력 평가'!$G$4:$G$8,"실패")</f>
+        <f>COUNTIF('인력 평가'!$G$4:$G$9,"실패")</f>
         <v>0</v>
       </c>
       <c r="E5" s="21">
-        <f>COUNTIF('인력 평가'!$G$4:$G$8,"오류")</f>
+        <f>COUNTIF('인력 평가'!$G$4:$G$9,"오류")</f>
         <v>0</v>
       </c>
       <c r="F5" s="21">
-        <f>COUNTIF('인력 평가'!$G$4:$G$8,"보류")</f>
+        <f>COUNTIF('인력 평가'!$G$4:$G$9,"보류")</f>
         <v>0</v>
       </c>
       <c r="G5" s="21">
-        <f>COUNTIF('인력 평가'!$G$4:$G$8,"확인 불가")</f>
+        <f>COUNTIF('인력 평가'!$G$4:$G$9,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H5" s="21">
-        <f>COUNTIF('인력 평가'!$G$4:$G$8,"문의")</f>
+        <f>COUNTIF('인력 평가'!$G$4:$G$9,"문의")</f>
         <v>0</v>
       </c>
       <c r="I5" s="21">
-        <f>COUNTBLANK('인력 평가'!$G$4:$G$8)</f>
-        <v>5</v>
+        <f>COUNTBLANK('인력 평가'!$G$4:$G$9)</f>
+        <v>6</v>
       </c>
       <c r="J5" s="22">
         <f>IF(B5=0,0,(B5-I5)/B5)</f>
@@ -1616,36 +1607,36 @@
         </is>
       </c>
       <c r="B6" s="21">
-        <f>COUNTA('평가 현황·설정'!$A$4:$A$5)</f>
-        <v>2</v>
+        <f>COUNTA('평가 현황·설정'!$A$4:$A$8)</f>
+        <v>5</v>
       </c>
       <c r="C6" s="21">
-        <f>COUNTIF('평가 현황·설정'!$G$4:$G$5,"성공")</f>
+        <f>COUNTIF('평가 현황·설정'!$G$4:$G$8,"성공")</f>
         <v>0</v>
       </c>
       <c r="D6" s="21">
-        <f>COUNTIF('평가 현황·설정'!$G$4:$G$5,"실패")</f>
+        <f>COUNTIF('평가 현황·설정'!$G$4:$G$8,"실패")</f>
         <v>0</v>
       </c>
       <c r="E6" s="21">
-        <f>COUNTIF('평가 현황·설정'!$G$4:$G$5,"오류")</f>
+        <f>COUNTIF('평가 현황·설정'!$G$4:$G$8,"오류")</f>
         <v>0</v>
       </c>
       <c r="F6" s="21">
-        <f>COUNTIF('평가 현황·설정'!$G$4:$G$5,"보류")</f>
+        <f>COUNTIF('평가 현황·설정'!$G$4:$G$8,"보류")</f>
         <v>0</v>
       </c>
       <c r="G6" s="21">
-        <f>COUNTIF('평가 현황·설정'!$G$4:$G$5,"확인 불가")</f>
+        <f>COUNTIF('평가 현황·설정'!$G$4:$G$8,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H6" s="21">
-        <f>COUNTIF('평가 현황·설정'!$G$4:$G$5,"문의")</f>
+        <f>COUNTIF('평가 현황·설정'!$G$4:$G$8,"문의")</f>
         <v>0</v>
       </c>
       <c r="I6" s="21">
-        <f>COUNTBLANK('평가 현황·설정'!$G$4:$G$5)</f>
-        <v>2</v>
+        <f>COUNTBLANK('평가 현황·설정'!$G$4:$G$8)</f>
+        <v>5</v>
       </c>
       <c r="J6" s="22">
         <f>IF(B6=0,0,(B6-I6)/B6)</f>
@@ -1655,40 +1646,40 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>예산 총괄표</t>
+          <t>예산 기준 설정</t>
         </is>
       </c>
       <c r="B7" s="21">
-        <f>COUNTA('예산 총괄표'!$A$4:$A$8)</f>
-        <v>5</v>
+        <f>COUNTA('예산 기준 설정'!$A$4:$A$6)</f>
+        <v>3</v>
       </c>
       <c r="C7" s="21">
-        <f>COUNTIF('예산 총괄표'!$G$4:$G$8,"성공")</f>
+        <f>COUNTIF('예산 기준 설정'!$G$4:$G$6,"성공")</f>
         <v>0</v>
       </c>
       <c r="D7" s="21">
-        <f>COUNTIF('예산 총괄표'!$G$4:$G$8,"실패")</f>
+        <f>COUNTIF('예산 기준 설정'!$G$4:$G$6,"실패")</f>
         <v>0</v>
       </c>
       <c r="E7" s="21">
-        <f>COUNTIF('예산 총괄표'!$G$4:$G$8,"오류")</f>
+        <f>COUNTIF('예산 기준 설정'!$G$4:$G$6,"오류")</f>
         <v>0</v>
       </c>
       <c r="F7" s="21">
-        <f>COUNTIF('예산 총괄표'!$G$4:$G$8,"보류")</f>
+        <f>COUNTIF('예산 기준 설정'!$G$4:$G$6,"보류")</f>
         <v>0</v>
       </c>
       <c r="G7" s="21">
-        <f>COUNTIF('예산 총괄표'!$G$4:$G$8,"확인 불가")</f>
+        <f>COUNTIF('예산 기준 설정'!$G$4:$G$6,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H7" s="21">
-        <f>COUNTIF('예산 총괄표'!$G$4:$G$8,"문의")</f>
+        <f>COUNTIF('예산 기준 설정'!$G$4:$G$6,"문의")</f>
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <f>COUNTBLANK('예산 총괄표'!$G$4:$G$8)</f>
-        <v>5</v>
+        <f>COUNTBLANK('예산 기준 설정'!$G$4:$G$6)</f>
+        <v>3</v>
       </c>
       <c r="J7" s="22">
         <f>IF(B7=0,0,(B7-I7)/B7)</f>
@@ -1698,40 +1689,40 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>예산 기준 설정</t>
+          <t>예산 총괄표</t>
         </is>
       </c>
       <c r="B8" s="21">
-        <f>COUNTA('예산 기준 설정'!$A$4:$A$6)</f>
-        <v>3</v>
+        <f>COUNTA('예산 총괄표'!$A$4:$A$12)</f>
+        <v>9</v>
       </c>
       <c r="C8" s="21">
-        <f>COUNTIF('예산 기준 설정'!$G$4:$G$6,"성공")</f>
+        <f>COUNTIF('예산 총괄표'!$G$4:$G$12,"성공")</f>
         <v>0</v>
       </c>
       <c r="D8" s="21">
-        <f>COUNTIF('예산 기준 설정'!$G$4:$G$6,"실패")</f>
+        <f>COUNTIF('예산 총괄표'!$G$4:$G$12,"실패")</f>
         <v>0</v>
       </c>
       <c r="E8" s="21">
-        <f>COUNTIF('예산 기준 설정'!$G$4:$G$6,"오류")</f>
+        <f>COUNTIF('예산 총괄표'!$G$4:$G$12,"오류")</f>
         <v>0</v>
       </c>
       <c r="F8" s="21">
-        <f>COUNTIF('예산 기준 설정'!$G$4:$G$6,"보류")</f>
+        <f>COUNTIF('예산 총괄표'!$G$4:$G$12,"보류")</f>
         <v>0</v>
       </c>
       <c r="G8" s="21">
-        <f>COUNTIF('예산 기준 설정'!$G$4:$G$6,"확인 불가")</f>
+        <f>COUNTIF('예산 총괄표'!$G$4:$G$12,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H8" s="21">
-        <f>COUNTIF('예산 기준 설정'!$G$4:$G$6,"문의")</f>
+        <f>COUNTIF('예산 총괄표'!$G$4:$G$12,"문의")</f>
         <v>0</v>
       </c>
       <c r="I8" s="21">
-        <f>COUNTBLANK('예산 기준 설정'!$G$4:$G$6)</f>
-        <v>3</v>
+        <f>COUNTBLANK('예산 총괄표'!$G$4:$G$12)</f>
+        <v>9</v>
       </c>
       <c r="J8" s="22">
         <f>IF(B8=0,0,(B8-I8)/B8)</f>
@@ -1746,7 +1737,7 @@
       </c>
       <c r="B9" s="24">
         <f>SUM(B5:B8)</f>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C9" s="24">
         <f>SUM(C5:C8)</f>
@@ -1774,7 +1765,7 @@
       </c>
       <c r="I9" s="24">
         <f>SUM(I5:I8)</f>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J9" s="25">
         <f>IF(B9=0,0,(B9-I9)/B9)</f>
@@ -1821,11 +1812,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -1845,7 +1836,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 새 탭에서 시작하세요.</t>
+          <t>🗂 QA박안전6 계정으로 하고, QA하정수6 줄만 시크릿 창에서 봅니다. 평가와 상신은 내 부서(문화체육과) 칸에서만 합니다 — 평가 완료와 상신 기록은 지울 수 없어 서버에 남습니다.</t>
         </is>
       </c>
     </row>
@@ -1896,13 +1887,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="66" customHeight="1">
       <c r="A4" s="28" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1917,25 +1908,27 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>연도·부서를 바꾼다</t>
+          <t>① 메뉴로 들어간다
+② 평가 결과의 평가 사이클을 다른 연도로 바꿨다가 되돌린다
+③ 부서를 몇 개 바꿔 본다</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>평가개요 · 결과 · 이력이 뜨고 조건대로 바뀐다</t>
+          <t>평가개요 · 평가 결과 · 평가 이력이 보인다. 사이클·부서를 바꾸면 표 머리와 대상자 줄이 그에 맞게 바뀐다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="111" customHeight="1">
       <c r="A5" s="28" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -1945,30 +1938,32 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>평가 등록</t>
+          <t>나를 평가자로 지정</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[평가등록] → [평가자 선택](조직도) → 점수 입력 → 저장</t>
+          <t>① 부서를 내 부서(문화체육과)로 바꾼다
+② 안전보건관리책임자 줄에서 평가자가 비어 있는 칸(상반기 또는 하반기)의 [평가자 선택]
+③ 왼쪽에서 재난안전과를 누르고 오른쪽에서 내 QA박안전6 계정만 골라 [… 선택] (남의 계정은 고르지 않는다 — 한 번 넣으면 바꾸는 버튼이 없다)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>평가자를 조직도에서 고르고, 저장하면 결과에 반영된다. 빈 칸이면 막힌다</t>
+          <t>평가자 칸에 내 QA박안전6(번호까지) 이름이 정확히 보이고 옆 [평가등록] 버튼이 눌리는 상태가 된다. 조직도에 내 계정이 없거나 박안전 계정끼리 표시 이름이 같으면 «확인 불가»</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>QA하정수6(담당 공무원)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -1978,30 +1973,30 @@
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>결재 상신</t>
+          <t>배정된 평가자만 평가한다</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>[결재상신] → 결재선 지정 → 상신 → 화면을 다시 연다</t>
+          <t>QA하정수6 창에서 같은 화면을 새로고침하고 부서를 내 부서(문화체육과)로 바꿔 2번 칸을 본다</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>결재선(기안 · 검토 · 결재)을 다 채워야 상신된다. 위에 문서번호·결재일·결재선이 보인다</t>
+          <t>평가자 칸에 내 QA박안전6(번호까지) 이름이 보이고 [평가등록]이 흐려 눌리지 않는다</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="111" customHeight="1">
       <c r="A7" s="28" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>홍길동 → 김담양</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -2011,50 +2006,388 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>과장·군수는 상신하지 않는다</t>
+          <t>임시저장과 평가 완료</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>[결재상신]을 본다</t>
+          <t>① 2번 칸의 [평가등록]
+② 아무것도 고르지 않고 [임시저장]
+③ 2~3개 항목만 골라 [임시저장]
+④ 그 칸의 버튼을 다시 눌러 남은 항목을 고르되 한 항목만 «미흡», 나머지는 «양호»로 하고 [평가 완료]</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>버튼이 없거나, 누르면 «상신은 담당자가 합니다…»로 막힌다(상신 창이 열리면 실패)</t>
+          <t>② «판정한 항목이 없어 임시저장할 내용이 없습니다» ③ 칸의 버튼이 «진행 중 N/M»으로 바뀌고(토스트 문구는 따지지 않는다) 다시 열면 고른 값이 남아 있다 ④ 다 고르기 전에는 [평가 완료]가 눌리지 않는다. 완료하면 그 칸에 평가일자와 종합 «미흡»이 뜨고(미흡이 하나라도 있으면 미흡) 아래 평가 이력에 한 줄 생긴다</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="126" customHeight="1">
       <c r="A8" s="28" t="n">
         <v>5</v>
       </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 인력 평가</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>평가 결과 보고 상신</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>① 부서가 내 부서(문화체육과)인 채 평가개요의 [결재상신]
+② 미리보기를 보고 [온나라로 결재 상신]
+③ [＋ 검토]로 빈 칸을 하나 늘린 채 [상신]
+④ 늘린 칸을 [×]로 지우고, 검토·결재를 [조직도] &gt; 재난안전과에서 내 것이 아닌 박안전 계정 두 개로 고른 뒤 [상신]
+⑤ [결재상신]을 다시 연다</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>② 미리보기 «평가 결과 목록»에 4번 평가가 있다 ③ «지정하지 않은 단계가 N건 있습니다 — 조직도에서 결재자를 고르세요.»로 막힌다 ④ 상신되고 바로 결재완료(내부 처리)가 된다 ⑤ 이미 상신된 보고서라는 안내와 결재선(기안 → 검토 → 결재 세 계정)이 보인다</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="81" customHeight="1">
+      <c r="A9" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 인력 평가</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>평가 이력 조건</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>① 사이클 · 부서 · 구분 · 결과를 하나씩 바꿔 본다
+② 이름 칸에 4번에서 평가한 부서장 이름 일부를 넣고 [검색]
+③ [초기화]</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>조건에 맞는 줄만 남고 위 «완료된 평가 N건»이 줄 수와 같다. ②에서 4번 평가가 찾아진다. ③ 뒤 조건이 모두 «전체»로 돌아오고 이름 칸이 빈다</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:I9"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G4:G9">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
+      <formula>"성공"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
+      <formula>"실패"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="3">
+      <formula>"오류"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="4">
+      <formula>"보류"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="5">
+      <formula>"확인 불가"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="6">
+      <formula>"문의"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H9">
+    <cfRule type="expression" priority="7" dxfId="7">
+      <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="G4:G9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
+      <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>인력·예산 — 평가 현황·설정</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>🗂 QA박안전6 계정으로 하고, QA하정수6 줄만 시크릿 창에서 봅니다. 평가 항목은 모든 평가표가 같이 쓰므로 새로 저장하지 않고, 고친 것은 같은 줄에서 원래대로 되돌립니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>누구로</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>어디서</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>확인할 것</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>해 볼 것</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>이러면 성공</t>
+        </is>
+      </c>
+      <c r="G3" s="27" t="inlineStr">
+        <is>
+          <t>결과 ▼</t>
+        </is>
+      </c>
+      <c r="H3" s="27" t="inlineStr">
+        <is>
+          <t>메모 (실패·오류·문의일 때)</t>
+        </is>
+      </c>
+      <c r="I3" s="27" t="inlineStr">
+        <is>
+          <t>사진 (필요할 때 붙여넣기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="81" customHeight="1">
+      <c r="A4" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 평가 현황</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>반기별 진행 현황</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>연도 2026에서 ① [상반기]
+② [하반기]
+③ [전체]를 차례로 누르며 위 숫자 칸을 본다</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>누를 때마다 평가 기간과 대상자 · 완료 · 진행 중 · 미시작 숫자가 바뀐다. «완료» 칸의 진행률(%)이 완료 ÷ 대상자와 맞다(반올림). [전체]는 평가 기간이 «2026 연간 (상·하반기 합산)»이다</t>
+        </is>
+      </c>
+      <c r="G4" s="29" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="66" customHeight="1">
+      <c r="A5" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 평가 현황</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>① 안전보건관리책임자 카드의 [템플릿 →]
+② 뒤로 가서, 위에 마감 알림 줄이 있으면 [미시작 평가 시작 →]</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>① 평가 설정으로 가서 그 역할 칸이 잠깐 강조된다 ② 인력 평가로 간다. 알림 줄은 평가 기간 중 미시작이 있을 때만 나오므로, 없으면 ①만 보고 고른다</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="66" customHeight="1">
+      <c r="A6" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 평가 설정</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>항목명 없이는 추가되지 않는다</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>① 안전보건관리책임자 칸의 [항목 추가]
+② 항목명을 비운 채 [저장]
+③ [취소] (새 항목은 저장하지 않는다 — 지우는 기능이 없어 모든 평가표에 남는다)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>«항목명을 입력하세요.»가 뜨고 저장되지 않는다. [취소] 뒤 항목 수가 그대로다</t>
+        </is>
+      </c>
+      <c r="G6" s="29" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="141" customHeight="1">
+      <c r="A7" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 평가 설정</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>고치면 평가 화면에 반영된다</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>① 안전보건관리책임자 1번 항목 [편집]
+② 평가 기준 (가이드) 맨 끝에 «이혜린_확인»을 덧붙여 [저장] (다른 사람 글자가 붙어 있으면 건드리지 않는다)
+③ 인력 평가 화면의 평가 이력에서 4번에 완료한 평가 [보기] → 1번 항목 [세부평가기준]을 펼친다
+④ 평가 설정으로 돌아와 같은 항목을 [편집]해 내가 붙인 «이혜린_확인»만 지우고 [저장]</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>② «저장되었습니다 — 평가화면에 반영됩니다.» ③ 덧붙인 «이혜린_확인»이 보인다 ④ 내 글자가 사라진다(다른 사람 글자는 남아 있을 수 있다)</t>
+        </is>
+      </c>
+      <c r="G7" s="29" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="81" customHeight="1">
+      <c r="A8" s="28" t="n">
+        <v>11</v>
+      </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C8" s="30" t="inlineStr">
+          <t>QA하정수6(담당 공무원)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>인력·예산 &gt; 인력 평가</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>평가 이력 조건</t>
+          <t>기준값 설정 메뉴는 담당 공무원에게 닫혀 있다</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>주기 · 부서 · 역할 · 결과 + 이름 검색 → [초기화]</t>
+          <t>QA하정수6 창에서 인력·예산 메뉴를 누르고 왼쪽 메뉴 목록을 본다. 평가 설정·예산 기준 설정이 보이면 눌러 [항목 추가]·[원칙 등록·개정]을 눌러 본다(저장하지 않고 [취소])</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>조건대로 걸러지고 초기화하면 전체로 돌아온다</t>
+          <t>인력 평가 · 평가 현황 · 예산 총괄표는 있고, 평가 설정 · 예산 기준 설정은 없거나 들어가도 [항목 추가]·[원칙 등록·개정]이 막힌다. 메뉴가 보이고 버튼도 눌리면 FAIL로 두고 무엇이 눌렸는지 메모에 적는다</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
@@ -2102,18 +2435,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -2126,14 +2459,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>인력·예산 — 평가 현황·설정</t>
+          <t>인력·예산 — 예산 기준 설정</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 어느 탭에서 해도 됩니다.</t>
+          <t>🗂 QA박안전6 계정으로 합니다. 원칙·예산 항목·점검 대상은 모두가 같이 쓰는 기준값이라 내 이름을 붙여 만들고, 지울 수 있는 것은 같은 줄에서 지웁니다. 내 부서 점검 대상은 예산 총괄표에서 쓰므로 남겨 둡니다.</t>
         </is>
       </c>
     </row>
@@ -2184,576 +2517,110 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="96" customHeight="1">
       <c r="A4" s="28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>인력·예산 &gt; 평가 현황</t>
+          <t>인력·예산 &gt; 예산 기준 설정</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>진행 현황</t>
+          <t>원칙 등록</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>[상반기] · [하반기] · [전체] → [평가 시작 →]</t>
+          <t>① [원칙 등록·개정]
+② 빈 채로 [저장]
+③ 제목에 «이혜린_예산 원칙»만 넣고 [저장]
+④ 시행일을 2000-01-01로 넣고 [저장] (옛 날짜로 넣어야 지금 원칙을 밀어내지 않는다 — 원칙은 지우는 기능이 없다)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>진행률이 바뀌고 평가 시작은 인력 평가로 간다</t>
+          <t>② «제목을 입력하세요.» ③ «시행일을 입력하세요.» ④ «원칙 문서가 개정 등록되었습니다.»가 뜨고 아래 개정 이력 표에 내 제목이 보인다(현행 원칙 칸은 다른 사람 등록에 따라 바뀔 수 있으니 판정하지 않는다)</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="51" customHeight="1">
+    <row r="5" ht="126" customHeight="1">
       <c r="A5" s="28" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>인력·예산 &gt; 평가 설정</t>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 예산 기준 설정</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>항목 추가·편집</t>
+          <t>예산 항목 추가·수정·삭제</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[항목 추가] → 빈 채로 저장 → 채워서 → 한 항목 [편집] 저장 → 인력 평가 화면을 본다</t>
+          <t>① [+ 대분류 추가] → 빈 채로 [확인]
+② «이혜린_대분류»로 [확인]
+③ 그 줄의 [+ 하위] → «이혜린_하위»로 [확인]
+④ 하위 줄 [수정] → «이혜린_하위2»로 [확인]
+⑤ «이혜린_대분류» 줄 [삭제]
+⑥ «이혜린_하위2» 줄 [삭제] → «이혜린_대분류» 줄 [삭제]</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>빈 채로는 «항목명을 입력하세요.» 저장하면 «저장되었습니다 — 평가화면에 반영됩니다.», 인력 평가에 실제로 보인다</t>
+          <t>① «항목명을 입력하세요.» ②~④ «저장되었습니다.»와 함께 트리에 보이고 이름이 바뀐다 ⑤ «하위 항목이 있어 삭제할 수 없습니다. 하위 항목을 먼저 삭제하세요.» ⑥ «항목이 삭제되었습니다.»와 함께 둘 다 사라진다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-  </sheetData>
-  <autoFilter ref="A3:I5"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="G4:G5">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
-      <formula>"성공"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
-      <formula>"실패"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="3">
-      <formula>"오류"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="4">
-      <formula>"보류"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="5">
-      <formula>"확인 불가"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="6">
-      <formula>"문의"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H5">
-    <cfRule type="expression" priority="7" dxfId="7">
-      <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="G4:G5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
-      <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0070AD47"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>인력·예산 — 예산 총괄표</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
-        <is>
-          <t>🗂 새 탭에서 시작하세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>누구로</t>
-        </is>
-      </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>어디서</t>
-        </is>
-      </c>
-      <c r="D3" s="19" t="inlineStr">
-        <is>
-          <t>확인할 것</t>
-        </is>
-      </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>해 볼 것</t>
-        </is>
-      </c>
-      <c r="F3" s="19" t="inlineStr">
-        <is>
-          <t>이러면 성공</t>
-        </is>
-      </c>
-      <c r="G3" s="27" t="inlineStr">
-        <is>
-          <t>결과 ▼</t>
-        </is>
-      </c>
-      <c r="H3" s="27" t="inlineStr">
-        <is>
-          <t>메모 (실패·오류·문의일 때)</t>
-        </is>
-      </c>
-      <c r="I3" s="27" t="inlineStr">
-        <is>
-          <t>사진 (필요할 때 붙여넣기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>인력·예산 &gt; 예산 총괄표</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>화면과 합계</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>연도 · 유형 · 상태 조건을 바꾼다</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>총 편성액·집행액·집행률이 표 합계와 같고 조건대로 바뀐다</t>
-        </is>
-      </c>
-      <c r="G4" s="29" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>인력·예산 &gt; 예산 총괄표</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>점검표 만들기</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[+ 점검표 생성] → 대상 없이 → 골라서 생성</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>대상이 없으면 «대상을 선택하세요.» 만들면 «작성중»으로 추가된다</t>
-        </is>
-      </c>
-      <c r="G5" s="29" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="51" customHeight="1">
+    <row r="6" ht="81" customHeight="1">
       <c r="A6" s="28" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
         <is>
-          <t>인력·예산 &gt; 예산 총괄표</t>
+          <t>인력·예산 &gt; 예산 기준 설정</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>상신 → 결재 결과 → 집행액</t>
+          <t>점검 대상 추가</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>작성중 점검표 → 상신 → 결재중에 고쳐 본다 → «결재 결과 회신 등록»으로 승인 → 집행액 입력</t>
+          <t>① 점검 대상 관리의 [+ 기관 추가]
+② 아무것도 고르지 않고 [선택 추가 (0건)]
+③ 검색 칸에 내 부서 이름 일부를 넣고 내 부서(문화체육과)를 체크 → [선택 추가 (1건)]
+④ [+ 시설 추가] → 목록만 보고 [취소]</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>결재중에는 잠긴다. 승인 완료 뒤에만 집행액·비고를 넣을 수 있다</t>
-        </is>
-      </c>
-      <c r="G6" s="29" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C7" s="30" t="inlineStr">
-        <is>
-          <t>인력·예산 &gt; 예산 총괄표</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>작성중 삭제</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>[삭제] → 확인</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>확인 뒤 사라진다. 결재중·승인완료 점검표에는 삭제 버튼이 없다</t>
-        </is>
-      </c>
-      <c r="G7" s="29" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>홍길동 → 김담양</t>
-        </is>
-      </c>
-      <c r="C8" s="30" t="inlineStr">
-        <is>
-          <t>인력·예산 &gt; 예산 총괄표</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>과장·군수는 보기만</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>총괄표와 점검표를 본다</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>만들기·삭제·상신·집행액 입력 버튼이 없거나 누르면 막힌다(저장되면 실패)</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:I8"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="G4:G8">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
-      <formula>"성공"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
-      <formula>"실패"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="3">
-      <formula>"오류"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="4">
-      <formula>"보류"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="5">
-      <formula>"확인 불가"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="6">
-      <formula>"문의"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H8">
-    <cfRule type="expression" priority="7" dxfId="7">
-      <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="G4:G8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
-      <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0070AD47"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>인력·예산 — 예산 기준 설정</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
-        <is>
-          <t>🗂 어느 탭에서 해도 됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>누구로</t>
-        </is>
-      </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>어디서</t>
-        </is>
-      </c>
-      <c r="D3" s="19" t="inlineStr">
-        <is>
-          <t>확인할 것</t>
-        </is>
-      </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>해 볼 것</t>
-        </is>
-      </c>
-      <c r="F3" s="19" t="inlineStr">
-        <is>
-          <t>이러면 성공</t>
-        </is>
-      </c>
-      <c r="G3" s="27" t="inlineStr">
-        <is>
-          <t>결과 ▼</t>
-        </is>
-      </c>
-      <c r="H3" s="27" t="inlineStr">
-        <is>
-          <t>메모 (실패·오류·문의일 때)</t>
-        </is>
-      </c>
-      <c r="I3" s="27" t="inlineStr">
-        <is>
-          <t>사진 (필요할 때 붙여넣기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>인력·예산 &gt; 예산 기준 설정</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>원칙 등록</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>[원칙 등록·개정] → 빈 채로 저장 → 채워서 저장</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>빈 채로는 «제목을 입력하세요.» 저장하면 목록에 반영된다</t>
-        </is>
-      </c>
-      <c r="G4" s="29" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>인력·예산 &gt; 예산 기준 설정</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>예산 항목</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[+ 대분류 추가] → [+ 하위] → [수정] → 하위가 있는 항목 [삭제]</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>추가·수정이 되고, 하위가 있으면 «하위 항목이 있어 삭제할 수 없습니다…»</t>
-        </is>
-      </c>
-      <c r="G5" s="29" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="51" customHeight="1">
-      <c r="A6" s="28" t="n">
-        <v>15</v>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t>인력·예산 &gt; 예산 기준 설정</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>점검 대상</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>[+ 기관 추가] → 안 고르고 추가 → 골라 추가 → 쓰고 있는 대상 [삭제] → [+ 시설 추가]</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>안 고르면 «추가할 대상을 선택하세요.», 쓰는 대상은 «…삭제할 수 없습니다.» 시설은 시설물 목록에서 고른다</t>
+          <t>② «추가할 대상을 선택하세요.» ③ «1건이 추가되었습니다.»와 함께 기관 목록에 내 부서가 생긴다(이미 «등록됨»이면 ③은 건너뛴다) ④ 시설물 대장의 시설이 종·등급과 함께 보인다</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
@@ -2801,6 +2668,441 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>인력·예산 — 예산 총괄표</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>🗂 QA박안전6 계정으로 합니다. 점검표는 내 부서(문화체육과) 대상으로만 만들고, 다른 사람 점검표는 열어 보기만 합니다. 승인완료된 점검표는 지울 수 없어 서버에 남습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>누구로</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>어디서</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>확인할 것</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>해 볼 것</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>이러면 성공</t>
+        </is>
+      </c>
+      <c r="G3" s="27" t="inlineStr">
+        <is>
+          <t>결과 ▼</t>
+        </is>
+      </c>
+      <c r="H3" s="27" t="inlineStr">
+        <is>
+          <t>메모 (실패·오류·문의일 때)</t>
+        </is>
+      </c>
+      <c r="I3" s="27" t="inlineStr">
+        <is>
+          <t>사진 (필요할 때 붙여넣기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="96" customHeight="1">
+      <c r="A4" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 예산 총괄표</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>점검표 만들기</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>① [+ 점검표 생성]
+② 대상을 고르지 않고 [생성]
+③ 연도 2026 · 대상구분 기관 · 대상 내 부서(문화체육과)를 고르고, 예방 항목 없이 [생성]
+④ 대분류 하나를 체크하고 [생성] (대상에 내 부서가 없으면 14번을 먼저)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>② «대상을 선택하세요.» ③ «예방 항목을 1개 이상 선택하세요.» ④ 대분류를 체크하면 하위가 함께 체크된다. «점검표가 생성되었습니다.»와 함께 2026년 내 부서 점검표 상세가 «작성중»으로 열린다</t>
+        </is>
+      </c>
+      <c r="G4" s="29" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="66" customHeight="1">
+      <c r="A5" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 예산 총괄표</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>같은 해·같은 대상은 하나만</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>① [+ 점검표 생성]
+② 15번과 같이 2026 · 기관 · 내 부서, 대분류 하나로 [생성]
+③ 연도만 2025로 바꿔 [생성]</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>② «이미 2026년 문화체육과 점검표가 있습니다.»로 막힌다 ③ 2025년 내 부서 점검표가 «작성중»으로 만들어진다</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="66" customHeight="1">
+      <c r="A6" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 예산 총괄표</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>작성중 점검표 삭제</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>① [← 목록]으로 가서 연도를 2025로 둔다
+② 16번에서 만든 2025년 내 부서 줄의 [삭제] → 확인 창에서 [취소]
+③ 다시 [삭제] → [확인]</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>확인 창이 먼저 묻고, [취소]하면 그대로다. [확인]하면 «점검표가 삭제되었습니다.»와 함께 목록에서 사라진다</t>
+        </is>
+      </c>
+      <c r="G6" s="29" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="96" customHeight="1">
+      <c r="A7" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 예산 총괄표</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>편성액 없이는 상신되지 않는다</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>① 15번의 2026년 내 부서 점검표를 [조회]로 연다
+② 편성액을 넣지 않고 [온나라 결재 상신]
+③ 결재선 창에서 검토·결재를 [조직도] &gt; 재난안전과에서 내 것이 아닌 박안전 계정 두 개로 고른 뒤 [상신]</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>«편성액 합계가 0원인 점검표는 상신할 수 없습니다.»로 막히고 상태는 «작성중» 그대로다</t>
+        </is>
+      </c>
+      <c r="G7" s="29" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 예산 총괄표</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>상신하면 결재가 바로 끝난다</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>① 18번 점검표에서 항목마다 편성액을 넣는다
+② [온나라 결재 상신] → 결재선이 18번에 고른 그대로인지 보고(비었으면 같은 방식으로 고른다) [상신] → [확인]</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>① 칸마다 «저장됨» ② 문서번호가 붙고 상태가 바로 «승인완료»(내부 처리)다</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 예산 총괄표</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>결재 상태 창</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>① 같은 점검표의 결재 상태 창을 연다
+② [이력]</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>결재완료 · «내부 처리»로 보이고 19번 결재선이 남아 있다. 결과를 옮겨 적는 버튼은 없다. 이력에 결재 상신이 처리자(QA박안전6 계정)와 함께 있다</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="81" customHeight="1">
+      <c r="A10" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 예산 총괄표</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>승인 뒤 집행액 입력</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>① 항목마다 집행액·비고를 넣는다
+② 편성액 칸을 고쳐 본다
+③ [← 목록]에서 이 점검표 줄을 본다</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>«승인 완료 — 집행액·비고는 계속 입력할 수 있습니다. (편성액은 잠금)»이 보인다. 집행액을 넣으면 «저장됨»과 함께 집행률·합계가 바로 바뀐다. 편성액 칸은 잠겨 있다. 목록의 이 줄은 «승인완료»이고 [삭제]가 없다</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="81" customHeight="1">
+      <c r="A11" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 예산 총괄표</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>합계와 조건</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>① 연도를 2026으로 둔다
+② 대상구분(기관·시설)과 상태(작성중·결재중·승인완료·반려)를 바꿔 본다
+③ 위 총 편성액 · 총 집행액 · 집행률 카드를 표 맨 아래 합계 줄과 비교한다</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>카드의 금액·집행률이 합계 줄과 같고 조건을 바꾸면 함께 바뀐다. 총 편성액 카드 아래 «2026년 점검표 N건»이 표 줄 수와 같다. 상태를 «승인완료»로 거르면 내 점검표가 있다</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="51" customHeight="1">
+      <c r="A12" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 예산 기준 설정</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>점검표가 쓰는 대상은 못 지운다</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>점검 대상 관리의 기관 목록에서 내 부서(문화체육과) 줄의 [삭제]</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>줄에 «사용 중»이 붙어 있고 «점검표에서 사용 중인 대상은 삭제할 수 없습니다.»가 뜨며 줄이 남는다</t>
+        </is>
+      </c>
+      <c r="G12" s="29" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:I12"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G4:G12">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
+      <formula>"성공"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
+      <formula>"실패"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="3">
+      <formula>"오류"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="4">
+      <formula>"보류"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="5">
+      <formula>"확인 불가"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="6">
+      <formula>"문의"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H12">
+    <cfRule type="expression" priority="7" dxfId="7">
+      <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="G4:G12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
+      <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2878,7 +3180,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
